--- a/docs/datasets/dataset_sources.xlsx
+++ b/docs/datasets/dataset_sources.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\varun\Harbinger\docs\datasets\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88C18131-7BC8-4000-A2B1-F5CBCDC2141D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="30624" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18,15 +24,106 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+  <si>
+    <t>Dataset</t>
+  </si>
+  <si>
+    <t>Official Source</t>
+  </si>
+  <si>
+    <t>Paper Source</t>
+  </si>
+  <si>
+    <t>Download URL</t>
+  </si>
+  <si>
+    <t>Access Status</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>Microsoft Philly</t>
+  </si>
+  <si>
+    <t>Alibaba Cluster Trace 2018</t>
+  </si>
+  <si>
+    <t>Helios</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google Cluster Trace </t>
+  </si>
+  <si>
+    <r>
+      <t>GitHub (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>msr-fiddle/philly-traces</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <t>USENIX ATC '19 ("Analysis of Large-Scale Multi-Tenant GPU Clusters...")</t>
+  </si>
+  <si>
+    <t>https://github.com/msr-fiddle/philly-traces/raw/master/trace-data.tar.gz</t>
+  </si>
+  <si>
+    <t>Open (CC-BY-4.0)</t>
+  </si>
+  <si>
+    <t>Contains detailed per-minute GPU, CPU, and memory utilization metrics.</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
     </font>
   </fonts>
   <fills count="2">
@@ -46,16 +143,42 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -66,6 +189,21 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F7807547-AF4E-4F87-8F5E-266FBF6968D6}" name="Table1" displayName="Table1" ref="B2:G6" totalsRowShown="0" headerRowDxfId="0">
+  <autoFilter ref="B2:G6" xr:uid="{F7807547-AF4E-4F87-8F5E-266FBF6968D6}"/>
+  <tableColumns count="6">
+    <tableColumn id="1" xr3:uid="{8F3A9A7E-8C96-4377-8B9F-F9D2637E70BA}" name="Dataset"/>
+    <tableColumn id="2" xr3:uid="{ECB803B5-D076-48E4-88DE-EF3A2122A1AB}" name="Official Source"/>
+    <tableColumn id="3" xr3:uid="{2066CB21-0CD9-4614-91B1-9A6430DA990E}" name="Paper Source"/>
+    <tableColumn id="4" xr3:uid="{D0AF0F99-23C8-4855-A4DC-32B3F13EB515}" name="Download URL"/>
+    <tableColumn id="5" xr3:uid="{CCFC2FF7-42ED-4CCE-A4F5-415F57D2F00B}" name="Access Status"/>
+    <tableColumn id="6" xr3:uid="{7A82506B-1782-4F3F-B690-83006343EBE7}" name="Notes"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -330,10 +468,81 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="B2:G6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="24.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="65" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="68.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="67" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:7">
+      <c r="B2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="2:7">
+      <c r="B3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="2:7">
+      <c r="B4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="2:7">
+      <c r="B5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="2:7">
+      <c r="B6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="E3" r:id="rId1" xr:uid="{962CA930-B6AF-4C7D-BDF3-53D0C8B58A35}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId2"/>
+  <tableParts count="1">
+    <tablePart r:id="rId3"/>
+  </tableParts>
 </worksheet>
 </file>